--- a/public/sample_material_import.xlsx
+++ b/public/sample_material_import.xlsx
@@ -124,7 +124,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -134,13 +134,28 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F9B3A"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -155,8 +170,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,45 +479,45 @@
   <cols>
     <col min="1" max="1" width="34.135" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="34.135" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" customHeight="1" ht="26">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/public/sample_material_import.xlsx
+++ b/public/sample_material_import.xlsx
@@ -2,9 +2,73 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M.KELUAR" sheetId="1" r:id="R3e2d6821e86148fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M.KELUAR" sheetId="1" r:id="R75de9eb602154ddb"/>
   </x:sheets>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>tc={F7746546-57A7-4210-ABDA-777F8228E374}</x:author>
+    <x:author>tc={AC2E1521-E74C-47EA-A918-BEAB0179BE97}</x:author>
+    <x:author>tc={23AC2DDA-63F2-4FFB-85F3-3E190B8347A0}</x:author>
+    <x:author>tc={C77025AD-2AAB-43ED-8760-48B37E860BFA}</x:author>
+    <x:author>tc={1428343F-2A46-4C3E-B9B1-6362A41E52A6}</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="A1" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tanggal transaksi. Gunakan tanggal Excel atau format YYYY-MM-DD.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D1" authorId="1">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nama staf yang bertanggung jawab mencatat data.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G1" authorId="2">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kode material wajib unik dan menggunakan pola yang konsisten.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I1" authorId="3">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Jumlah material yang keluar untuk rumah. Harus lebih dari 0.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L1" authorId="4">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Otomatis: Volume × Harga Satuan. Salin formula ke baris baru.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16,7 +80,7 @@
   <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
-    <x:numFmt numFmtId="202" formatCode="#,##0.##"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="3">
@@ -25,16 +89,15 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2A23"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF666666"/>
-      <x:name val="Carlito"/>
+      <x:name val="Aptos Display"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -51,7 +114,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2F0D9"/>
+        <x:fgColor rgb="FFEAF5E9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -75,64 +138,38 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -140,6 +177,33 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="User" id="{43D51D07-1E63-46EE-BE48-D254CF503363}"/>
+</xltc:personList>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaterialKeluarTable" displayName="MaterialKeluarTable" ref="A1:M3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="TANGGAL"/>
+    <x:tableColumn id="2" name="BULAN"/>
+    <x:tableColumn id="3" name="TAHUN"/>
+    <x:tableColumn id="4" name="PENANGGUNG JAWAB"/>
+    <x:tableColumn id="5" name="BLOK RUMAH"/>
+    <x:tableColumn id="6" name="KETERANGAN PEKERJAAN"/>
+    <x:tableColumn id="7" name="KODE BARANG"/>
+    <x:tableColumn id="8" name="NAMA BARANG"/>
+    <x:tableColumn id="9" name="VOLUME"/>
+    <x:tableColumn id="10" name="SATUAN"/>
+    <x:tableColumn id="11" name="HARGA SATUAN"/>
+    <x:tableColumn id="12" name="JUMLAH"/>
+    <x:tableColumn id="13" name="TOKO/SUPPLIER"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -333,201 +397,175 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="A1" dT="2026-08-31T00:46:43.608" personId="{43D51D07-1E63-46EE-BE48-D254CF503363}" id="{F7746546-57A7-4210-ABDA-777F8228E374}">
+    <xltc:text>Tanggal transaksi. Gunakan tanggal Excel atau format YYYY-MM-DD.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="D1" dT="2026-08-31T00:46:43.609" personId="{43D51D07-1E63-46EE-BE48-D254CF503363}" id="{AC2E1521-E74C-47EA-A918-BEAB0179BE97}">
+    <xltc:text>Nama staf yang bertanggung jawab mencatat data.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="G1" dT="2026-08-31T00:46:43.609" personId="{43D51D07-1E63-46EE-BE48-D254CF503363}" id="{23AC2DDA-63F2-4FFB-85F3-3E190B8347A0}">
+    <xltc:text>Kode material wajib unik dan menggunakan pola yang konsisten.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="I1" dT="2026-08-31T00:46:43.609" personId="{43D51D07-1E63-46EE-BE48-D254CF503363}" id="{C77025AD-2AAB-43ED-8760-48B37E860BFA}">
+    <xltc:text>Jumlah material yang keluar untuk rumah. Harus lebih dari 0.</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="L1" dT="2026-08-31T00:46:43.609" personId="{43D51D07-1E63-46EE-BE48-D254CF503363}" id="{1428343F-2A46-4C3E-B9B1-6362A41E52A6}">
+    <xltc:text>Otomatis: Volume × Harga Satuan. Salin formula ke baris baru.</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="16" t="str">
-        <x:v> </x:v>
-      </x:c>
-      <x:c r="B1" s="16" t="str">
+    <x:row r="1" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>TANGGAL</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
         <x:v>BULAN</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>TAHUN</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="E1" s="16" t="str">
-        <x:v>PENGAMBIL</x:v>
-      </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="D1" s="7" t="str">
+        <x:v>PENANGGUNG JAWAB</x:v>
+      </x:c>
+      <x:c r="E1" s="7" t="str">
         <x:v>BLOK RUMAH</x:v>
       </x:c>
-      <x:c r="G1" s="16" t="str">
+      <x:c r="F1" s="7" t="str">
         <x:v>KETERANGAN PEKERJAAN</x:v>
       </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="G1" s="7" t="str">
         <x:v>KODE BARANG</x:v>
       </x:c>
-      <x:c r="I1" s="16" t="str">
+      <x:c r="H1" s="7" t="str">
         <x:v>NAMA BARANG</x:v>
       </x:c>
-      <x:c r="J1" s="16" t="str">
+      <x:c r="I1" s="7" t="str">
         <x:v>VOLUME</x:v>
       </x:c>
-      <x:c r="K1" s="16" t="str">
+      <x:c r="J1" s="7" t="str">
         <x:v>SATUAN</x:v>
       </x:c>
-      <x:c r="L1" s="16" t="str">
+      <x:c r="K1" s="7" t="str">
         <x:v>HARGA SATUAN</x:v>
       </x:c>
-      <x:c r="M1" s="16" t="str">
+      <x:c r="L1" s="7" t="str">
         <x:v>JUMLAH</x:v>
       </x:c>
-      <x:c r="N1" s="16" t="str">
+      <x:c r="M1" s="7" t="str">
         <x:v>TOKO/SUPPLIER</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="B2" s="17" t="str"/>
-      <x:c r="C2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="D2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="E2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="F2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="G2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="H2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="I2" s="17" t="str">
-        <x:v>*LINK</x:v>
-      </x:c>
-      <x:c r="J2" s="17" t="str">
-        <x:v>*DI ISI</x:v>
-      </x:c>
-      <x:c r="K2" s="17" t="str">
-        <x:v>*LINK</x:v>
-      </x:c>
-      <x:c r="L2" s="17" t="str">
-        <x:v>*LINK</x:v>
-      </x:c>
-      <x:c r="M2" s="17" t="str">
-        <x:v>*LINK</x:v>
-      </x:c>
-      <x:c r="N2" s="17" t="str">
-        <x:v>*LINK</x:v>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>SEPTEMBER</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>Andi Pratama</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>Blok G-01</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>Pekerjaan pasangan dinding</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>MAT-TPL-001</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>Bata Ringan AAC 10 cm</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>buah</x:v>
+      </x:c>
+      <x:c r="K2" s="12" t="n">
+        <x:v>12500</x:v>
+      </x:c>
+      <x:c r="L2" s="12" t="n">
+        <x:f>I2*K2</x:f>
+        <x:v>6250000</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="str">
+        <x:v>CV. Sumber Bangunan</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="18" t="n">
-        <x:v>46265</x:v>
-      </x:c>
-      <x:c r="B3" s="19" t="str">
-        <x:v>AGUSTUS</x:v>
-      </x:c>
-      <x:c r="C3" s="20" t="n">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>SEPTEMBER</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="E3" s="19" t="str">
-        <x:v>AGUS</x:v>
-      </x:c>
-      <x:c r="F3" s="19" t="str">
-        <x:v>Blok F-01</x:v>
-      </x:c>
-      <x:c r="G3" s="19" t="str">
-        <x:v>Pondasi Rumah Baru</x:v>
-      </x:c>
-      <x:c r="H3" s="19" t="str">
-        <x:v>BL510</x:v>
-      </x:c>
-      <x:c r="I3" s="19" t="str">
-        <x:v>Semen Portland Baru 2026</x:v>
-      </x:c>
-      <x:c r="J3" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K3" s="19" t="str">
+      <x:c r="D3" s="8" t="str">
+        <x:v>Siti Rahma</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>Blok G-02</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="str">
+        <x:v>Pekerjaan plester dinding</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
+        <x:v>MAT-TPL-002</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="str">
+        <x:v>Semen Portland 50 kg</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="str">
         <x:v>sak</x:v>
       </x:c>
-      <x:c r="L3" s="22" t="n">
-        <x:v>95000</x:v>
-      </x:c>
-      <x:c r="M3" s="22" t="n">
-        <x:v>950000</x:v>
-      </x:c>
-      <x:c r="N3" s="19" t="str">
-        <x:v>CV. Bangun Jaya</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="18" t="n">
-        <x:v>46265</x:v>
-      </x:c>
-      <x:c r="B4" s="19" t="str">
-        <x:v>AGUSTUS</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="D4" s="19" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="E4" s="19" t="str">
-        <x:v>AGUS</x:v>
-      </x:c>
-      <x:c r="F4" s="19" t="str">
-        <x:v>Blok F-01</x:v>
-      </x:c>
-      <x:c r="G4" s="19" t="str">
-        <x:v>Dinding Rumah Baru</x:v>
-      </x:c>
-      <x:c r="H4" s="19" t="str">
-        <x:v>BL511</x:v>
-      </x:c>
-      <x:c r="I4" s="19" t="str">
-        <x:v>Bata Merah Dimaz</x:v>
-      </x:c>
-      <x:c r="J4" s="21" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K4" s="19" t="str">
-        <x:v>buah</x:v>
-      </x:c>
-      <x:c r="L4" s="22" t="n">
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="M4" s="22" t="n">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="N4" s="19" t="str">
+      <x:c r="K3" s="12" t="n">
+        <x:v>96000</x:v>
+      </x:c>
+      <x:c r="L3" s="12" t="n">
+        <x:f>I3*K3</x:f>
+        <x:v>2400000</x:v>
+      </x:c>
+      <x:c r="M3" s="8" t="str">
         <x:v>TB. Maju Bersama</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb18fe830d4d4349"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aef956e822e4a8c"/>
+  </x:tableParts>
 </x:worksheet>
 </file>